--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4168026</v>
+        <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
+        <v>95519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sluttning, 300 m ONO om gården Halmstad, Björnåsen, Boh</t>
+          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>304995.0286784032</v>
+        <v>304999.9714015288</v>
       </c>
       <c r="R3" t="n">
-        <v>6511326.951447706</v>
+        <v>6511331.908746853</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +878,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,269 +896,21 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89433238</v>
-      </c>
-      <c r="B4" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>304999.9714015288</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6511331.908746853</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Kjell Emanuelsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>89433229</v>
-      </c>
-      <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>304999.9714015288</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6511331.908746853</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
         </is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,12 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>304999.9714015288</v>
+        <v>305000</v>
       </c>
       <c r="R3" t="n">
-        <v>6511331.908746853</v>
+        <v>6511332</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +860,9 @@
           <t>1999-01-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89433229</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89433229</v>
+        <v>4168026</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>95510</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
+          <t>Sluttning, 300 m ONO om gården Halmstad, Björnåsen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>305000</v>
+        <v>304995.0286784032</v>
       </c>
       <c r="R3" t="n">
-        <v>6511332</v>
+        <v>6511326.951447706</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,14 +865,19 @@
           <t>1999-01-20</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-01-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,21 +891,235 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89433238</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97516</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>305000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6511332</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1999-01-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1999-01-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Evastina Blomgren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Kjell Emanuelsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89433229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>305000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6511332</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1999-01-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1999-01-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kjell Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
         </is>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4214665</v>
+        <v>4168026</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>304995.0286784032</v>
+        <v>304995</v>
       </c>
       <c r="R2" t="n">
-        <v>6511326.951447706</v>
+        <v>6511327</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +739,9 @@
           <t>1999-01-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4168026</v>
+        <v>4214665</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>304995.0286784032</v>
+        <v>304995</v>
       </c>
       <c r="R3" t="n">
-        <v>6511326.951447706</v>
+        <v>6511327</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +841,9 @@
           <t>1999-01-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,224 +872,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89433238</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97516</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>305000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6511332</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>89433229</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97522</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>300 m ONO om gården Halmstad, i sluttning, Björnåsen, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>305000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6511332</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tanum</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1999-01-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Kjell Emanuelsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63439-2023 artfynd.xlsx
+++ b/artfynd/A 63439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4168026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,8 +882,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4214665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>